--- a/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step2_dt.xlsx
+++ b/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step2_dt.xlsx
@@ -29,39 +29,39 @@
   </si>
   <si>
     <t>DT_001
-Các điều kiện chính đều thỏa mãn nên rule dẫn tới expected thành công.</t>
+Username</t>
   </si>
   <si>
     <t>DT_002
-C1=N (Username không rỗng) quyết định expected của rule.</t>
+Vui lòng điền vào trường này</t>
   </si>
   <si>
     <t>DT_003
-C2=N (Username không trùng) quyết định expected của rule.</t>
+tài khoản đã tồn tại trong hệ thống</t>
   </si>
   <si>
     <t>DT_004
-C3=N (Phone không rỗng) quyết định expected của rule.</t>
+Vui lòng điền vào trường này</t>
   </si>
   <si>
     <t>DT_005
-C4=N (Phone đúng định dạng) quyết định expected của rule.</t>
+Số điện thoại không đúng định dạng!</t>
   </si>
   <si>
     <t>DT_006
-C5=N (Password không rỗng) quyết định expected của rule.</t>
+Vui lòng điền vào trường này</t>
   </si>
   <si>
     <t>DT_007
-C6=N (Password độ dài hợp lệ) quyết định expected của rule.</t>
+Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
   </si>
   <si>
     <t>DT_008
-C7=N (ConfirmPassword không rỗng) quyết định expected của rule.</t>
+Vui lòng điền vào trường này</t>
   </si>
   <si>
     <t>DT_009
-C8=N (ConfirmPassword khớp Password) quyết định expected của rule.</t>
+mật khẩu không giống nhau</t>
   </si>
   <si>
     <t>C1 - Username không rỗng</t>
@@ -94,10 +94,10 @@
     <t>C6 - Password độ dài hợp lệ</t>
   </si>
   <si>
-    <t>C7 - ConfirmPassword không rỗng</t>
-  </si>
-  <si>
-    <t>C8 - ConfirmPassword khớp Password</t>
+    <t>C7 - PasswordConfirm không rỗng</t>
+  </si>
+  <si>
+    <t>C8 - PasswordConfirm khớp Password</t>
   </si>
   <si>
     <t>Kết quả / Hành động</t>
@@ -112,13 +112,13 @@
     <t>A2 - Thông báo tài khoản tồn tại: tài khoản đã tồn tại trong hệ thống</t>
   </si>
   <si>
-    <t>A3 - Thông báo số điện thoại không hợp lệ: Số điện thoại không hợp lệ</t>
-  </si>
-  <si>
-    <t>A4 - Thông báo mật khẩu độ dài không hợp lệ: Mật khẩu phải từ 8 đến 20 ký tự</t>
-  </si>
-  <si>
-    <t>A5 - Thông báo mật khẩu không khớp: Mật khẩu không khớp</t>
+    <t>A3 - Thông báo số điện thoại không hợp lệ: Số điện thoại không đúng định dạng!</t>
+  </si>
+  <si>
+    <t>A4 - Thông báo mật khẩu độ dài không hợp lệ: Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
+  </si>
+  <si>
+    <t>A5 - Thông báo mật khẩu không khớp: mật khẩu không giống nhau</t>
   </si>
   <si>
     <t>A6 - Thông báo đăng ký thành công: Username</t>
@@ -139,7 +139,13 @@
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -151,19 +157,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -191,7 +191,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -238,11 +238,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -254,27 +261,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -588,17 +598,17 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="45.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="45.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="28.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="28">
@@ -616,23 +626,23 @@
       <c r="J1" s="2"/>
       <c r="K1" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="34">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="34" customFormat="1" s="4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="34">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2"/>
@@ -644,456 +654,456 @@
       <c r="J3" s="2"/>
       <c r="K3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="55" customFormat="1" s="7">
-      <c r="A4" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="55" customFormat="1" s="4">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
-      <c r="A5" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
-      <c r="A6" s="10" t="s">
+      <c r="F5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21">
-      <c r="A7" s="10" t="s">
+      <c r="F6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21">
-      <c r="A8" s="10" t="s">
+      <c r="H7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="11" t="s">
+      <c r="D8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
-      <c r="A9" s="10" t="s">
+      <c r="H8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="11" t="s">
+      <c r="D9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
-      <c r="A10" s="10" t="s">
+      <c r="J9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="11" t="s">
+      <c r="D10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="11" t="s">
+      <c r="D11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
-      <c r="A12" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="11" t="s">
+      <c r="D12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75" customFormat="1" s="7">
-      <c r="A13" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25" customFormat="1" s="4">
+      <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="35.25">
-      <c r="A14" s="10" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="33">
+      <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11" t="s">
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11" t="s">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11" t="s">
+      <c r="I14" s="12"/>
+      <c r="J14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="35.25">
-      <c r="A15" s="10" t="s">
+      <c r="K14" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="33">
+      <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="35.25">
-      <c r="A16" s="10" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33">
+      <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="35.25">
-      <c r="A17" s="10" t="s">
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="47.25">
+      <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="35.25">
-      <c r="A18" s="10" t="s">
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33">
+      <c r="A18" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11" t="s">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="36">
-      <c r="A19" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25">
+      <c r="A19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="4">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
